--- a/downloads/Trainory_Third_Party_Vendor_Risk_Assessment.xlsx
+++ b/downloads/Trainory_Third_Party_Vendor_Risk_Assessment.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="Rbb0d26a706a94059"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessment" sheetId="2" r:id="Rd9757ec3b3954e2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="3" r:id="Rc1f97a4b8c834331"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="4" r:id="R9e633dadf1cc4689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R23413adfa8794e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessment" sheetId="2" r:id="R9ab9942343fa4049"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="3" r:id="R310bf0d6912140bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="4" r:id="R16f50ced81104d78"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +22,7 @@
     <x:numFmt numFmtId="202" formatCode="0"/>
     <x:numFmt numFmtId="203" formatCode="0.0"/>
   </x:numFmts>
-  <x:fonts count="20">
+  <x:fonts count="22">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -133,8 +133,20 @@
       <x:color rgb="FF0B2545"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -164,6 +176,66 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF8FAFC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EFF6"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -269,7 +341,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="123">
+  <x:cellXfs count="137">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -567,6 +639,48 @@
     <x:xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -577,7 +691,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -587,7 +701,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -597,7 +711,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -608,7 +722,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -618,7 +732,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -628,7 +742,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -639,7 +753,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -650,7 +764,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -660,7 +774,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -670,7 +784,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -681,7 +795,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -692,7 +806,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -702,7 +816,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -712,7 +826,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -868,7 +982,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R46fad713fdf54dbc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c8eb999d8b944a0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1145,17 +1259,35 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="61" t="str">
-        <x:v>Step 7 | Fictional wearable-data integration provider: VitaSync</x:v>
-      </x:c>
-      <x:c r="B2" s="61"/>
-      <x:c r="C2" s="61"/>
-      <x:c r="D2" s="61"/>
-      <x:c r="E2" s="61"/>
-      <x:c r="F2" s="61"/>
-      <x:c r="G2" s="61"/>
-      <x:c r="H2" s="61"/>
-      <x:c r="I2" s="61"/>
-      <x:c r="J2" s="61"/>
+        <x:v>Fictional wearable-data integration assessment</x:v>
+      </x:c>
+      <x:c r="B2" s="61" t="str">
+        <x:v>Fictional wearable-data integration assessment</x:v>
+      </x:c>
+      <x:c r="C2" s="61" t="str">
+        <x:v>Fictional wearable-data integration assessment</x:v>
+      </x:c>
+      <x:c r="D2" s="61" t="str">
+        <x:v>Fictional wearable-data integration assessment</x:v>
+      </x:c>
+      <x:c r="E2" s="61" t="str">
+        <x:v>Fictional wearable-data integration assessment</x:v>
+      </x:c>
+      <x:c r="F2" s="61" t="str">
+        <x:v>Fictional wearable-data integration assessment</x:v>
+      </x:c>
+      <x:c r="G2" s="61" t="str">
+        <x:v>Fictional wearable-data integration assessment</x:v>
+      </x:c>
+      <x:c r="H2" s="61" t="str">
+        <x:v>Fictional wearable-data integration assessment</x:v>
+      </x:c>
+      <x:c r="I2" s="61" t="str">
+        <x:v>Fictional wearable-data integration assessment</x:v>
+      </x:c>
+      <x:c r="J2" s="61" t="str">
+        <x:v>Fictional wearable-data integration assessment</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="62"/>
@@ -1590,17 +1722,35 @@
     </x:row>
     <x:row r="30" ht="32" customHeight="1">
       <x:c r="A30" s="82" t="str">
-        <x:v>Portfolio note: VitaSync and all evidence, responses, findings, and decisions in this workbook are fictional and intended only to demonstrate a vendor-risk assessment process.</x:v>
-      </x:c>
-      <x:c r="B30" s="82"/>
-      <x:c r="C30" s="82"/>
-      <x:c r="D30" s="82"/>
-      <x:c r="E30" s="82"/>
-      <x:c r="F30" s="82"/>
-      <x:c r="G30" s="82"/>
-      <x:c r="H30" s="82"/>
-      <x:c r="I30" s="82"/>
-      <x:c r="J30" s="82"/>
+        <x:v>Case study note: VitaSync and all evidence, responses, findings, and decisions are fictional.</x:v>
+      </x:c>
+      <x:c r="B30" s="82" t="str">
+        <x:v>Case study note: VitaSync and all evidence, responses, findings, and decisions are fictional.</x:v>
+      </x:c>
+      <x:c r="C30" s="82" t="str">
+        <x:v>Case study note: VitaSync and all evidence, responses, findings, and decisions are fictional.</x:v>
+      </x:c>
+      <x:c r="D30" s="82" t="str">
+        <x:v>Case study note: VitaSync and all evidence, responses, findings, and decisions are fictional.</x:v>
+      </x:c>
+      <x:c r="E30" s="82" t="str">
+        <x:v>Case study note: VitaSync and all evidence, responses, findings, and decisions are fictional.</x:v>
+      </x:c>
+      <x:c r="F30" s="82" t="str">
+        <x:v>Case study note: VitaSync and all evidence, responses, findings, and decisions are fictional.</x:v>
+      </x:c>
+      <x:c r="G30" s="82" t="str">
+        <x:v>Case study note: VitaSync and all evidence, responses, findings, and decisions are fictional.</x:v>
+      </x:c>
+      <x:c r="H30" s="82" t="str">
+        <x:v>Case study note: VitaSync and all evidence, responses, findings, and decisions are fictional.</x:v>
+      </x:c>
+      <x:c r="I30" s="82" t="str">
+        <x:v>Case study note: VitaSync and all evidence, responses, findings, and decisions are fictional.</x:v>
+      </x:c>
+      <x:c r="J30" s="82" t="str">
+        <x:v>Case study note: VitaSync and all evidence, responses, findings, and decisions are fictional.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1624,7 +1774,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b6599a881a94cbe"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f6ea610eaf54bf2"/>
 </x:worksheet>
 </file>
 
@@ -3478,7 +3628,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89483131a3de4624"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd98ef80681b445b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4186,7 +4336,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f6ddb3e030e480a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra152a6a034094444"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4200,24 +4350,32 @@
     <x:col min="3" max="3" width="70" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="60" t="str">
-        <x:v>Reviewer Guide</x:v>
-      </x:c>
-      <x:c r="B1" s="60"/>
-      <x:c r="C1" s="60"/>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="135" t="str">
+        <x:v>Vendor Assessment Methodology</x:v>
+      </x:c>
+      <x:c r="B1" s="135" t="str">
+        <x:v>Vendor Assessment Methodology</x:v>
+      </x:c>
+      <x:c r="C1" s="135" t="str">
+        <x:v>Vendor Assessment Methodology</x:v>
+      </x:c>
       <x:c r="D1" s="60"/>
       <x:c r="E1" s="60"/>
       <x:c r="F1" s="60"/>
       <x:c r="G1" s="60"/>
       <x:c r="H1" s="60"/>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="61" t="str">
-        <x:v>How to use and explain the Trainory vendor-risk assessment</x:v>
-      </x:c>
-      <x:c r="B2" s="61"/>
-      <x:c r="C2" s="61"/>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="136" t="str">
+        <x:v>Review steps, scoring method, evidence requirements, and key terms</x:v>
+      </x:c>
+      <x:c r="B2" s="136" t="str">
+        <x:v>Review steps, scoring method, evidence requirements, and key terms</x:v>
+      </x:c>
+      <x:c r="C2" s="136" t="str">
+        <x:v>Review steps, scoring method, evidence requirements, and key terms</x:v>
+      </x:c>
       <x:c r="D2" s="61"/>
       <x:c r="E2" s="61"/>
       <x:c r="F2" s="61"/>
@@ -4236,7 +4394,7 @@
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="63" t="str">
-        <x:v>What this workbook demonstrates</x:v>
+        <x:v>PURPOSE</x:v>
       </x:c>
       <x:c r="B4" s="64"/>
       <x:c r="C4" s="64"/>
@@ -4248,7 +4406,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="73" t="str">
-        <x:v>This assessment shows how a GRC analyst scopes a high-risk vendor, asks control questions, evaluates evidence, scores gaps, documents findings, recommends treatments, and gives leadership a defensible approval decision. It also connects third-party risk to Trainory's risk register, access policy, incident-response plan, and NIST CSF 2.0 assessment.</x:v>
+        <x:v>Evaluates VitaSync's control environment, evidence, residual risk, and conditions for use.</x:v>
       </x:c>
       <x:c r="B5" s="74"/>
       <x:c r="C5" s="74"/>
@@ -4310,7 +4468,7 @@
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
       <x:c r="A11" s="63" t="str">
-        <x:v>Suggested review sequence</x:v>
+        <x:v>ASSESSMENT STRUCTURE</x:v>
       </x:c>
       <x:c r="B11" s="64"/>
       <x:c r="C11" s="64"/>
@@ -4328,7 +4486,7 @@
         <x:v>Area</x:v>
       </x:c>
       <x:c r="C12" s="71" t="str">
-        <x:v>What to explain</x:v>
+        <x:v>Content</x:v>
       </x:c>
       <x:c r="D12" s="62"/>
       <x:c r="E12" s="62"/>
@@ -4344,7 +4502,7 @@
         <x:v>Executive Summary</x:v>
       </x:c>
       <x:c r="C13" s="67" t="str">
-        <x:v>Explain why VitaSync is high risk and why the recommendation is conditional rather than a simple yes or no.</x:v>
+        <x:v>Business rationale, inherent risk, and conditional recommendation.</x:v>
       </x:c>
       <x:c r="D13" s="62"/>
       <x:c r="E13" s="62"/>
@@ -4360,7 +4518,7 @@
         <x:v>Assessment</x:v>
       </x:c>
       <x:c r="C14" s="67" t="str">
-        <x:v>Review the scoring method, vendor responses, evidence quality, and formula-driven risk flags.</x:v>
+        <x:v>Scoring method, responses, evidence quality, and formula-driven risk flags.</x:v>
       </x:c>
       <x:c r="D14" s="62"/>
       <x:c r="E14" s="62"/>
@@ -4376,7 +4534,7 @@
         <x:v>Findings</x:v>
       </x:c>
       <x:c r="C15" s="67" t="str">
-        <x:v>Show how a weak or missing control becomes a tracked risk with an owner, deadline, treatment, and residual risk.</x:v>
+        <x:v>Tracked risks with owners, deadlines, treatments, and residual ratings.</x:v>
       </x:c>
       <x:c r="D15" s="62"/>
       <x:c r="E15" s="62"/>
@@ -4392,7 +4550,7 @@
         <x:v>Decision</x:v>
       </x:c>
       <x:c r="C16" s="67" t="str">
-        <x:v>Explain that compensating controls and contract conditions reduce risk but do not erase uncertainty.</x:v>
+        <x:v>Compensating controls and contractual conditions supporting the decision.</x:v>
       </x:c>
       <x:c r="D16" s="62"/>
       <x:c r="E16" s="62"/>
@@ -4408,7 +4566,7 @@
         <x:v>Follow-up</x:v>
       </x:c>
       <x:c r="C17" s="67" t="str">
-        <x:v>Describe annual reassessment, event-driven review, evidence refresh, and closure validation.</x:v>
+        <x:v>Annual reassessment, event-driven review, evidence refresh, and closure validation.</x:v>
       </x:c>
       <x:c r="D17" s="62"/>
       <x:c r="E17" s="62"/>
@@ -4427,9 +4585,7 @@
       <x:c r="H18" s="62"/>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
-      <x:c r="A19" s="63" t="str">
-        <x:v>Interview-ready explanation</x:v>
-      </x:c>
+      <x:c r="A19" s="63"/>
       <x:c r="B19" s="64"/>
       <x:c r="C19" s="64"/>
       <x:c r="D19" s="64"/>
@@ -4439,9 +4595,7 @@
       <x:c r="H19" s="65"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="114" t="str">
-        <x:v>I assessed a fictional wearable-integration vendor that would process sensitive fitness and wellness data for Trainory. I weighted the questions based on business impact, reviewed the assumed evidence, calculated a control score, and converted significant gaps into formal findings. I recommended conditional approval because the vendor had useful baseline controls, but Trainory still needed stronger assurance, disaster-recovery evidence, data-deletion terms, and faster incident notification. I also assigned owners and deadlines so the decision could be monitored rather than treated as a one-time questionnaire.</x:v>
-      </x:c>
+      <x:c r="A20" s="114"/>
       <x:c r="B20" s="115"/>
       <x:c r="C20" s="115"/>
       <x:c r="D20" s="115"/>
@@ -4632,7 +4786,7 @@
     </x:row>
     <x:row r="36" ht="30" customHeight="1">
       <x:c r="A36" s="82" t="str">
-        <x:v>Portfolio disclaimer: VitaSync is fictional. This workbook is an educational artifact, not an actual vendor certification, audit, legal opinion, or purchasing decision.</x:v>
+        <x:v>Case study note: Trainory, VitaSync, and all assessment data are fictional.</x:v>
       </x:c>
       <x:c r="B36" s="82"/>
       <x:c r="C36" s="82"/>
@@ -4644,8 +4798,6 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
     <x:mergeCell ref="A4:H4"/>
     <x:mergeCell ref="A5:H9"/>
     <x:mergeCell ref="A11:H11"/>
@@ -4653,6 +4805,8 @@
     <x:mergeCell ref="A20:H25"/>
     <x:mergeCell ref="A27:H27"/>
     <x:mergeCell ref="A36:H36"/>
+    <x:mergeCell ref="A1:C1"/>
+    <x:mergeCell ref="A2:C2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
